--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,6 +810,122 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126063813</v>
+      </c>
+      <c r="B3" t="n">
+        <v>45051</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102918</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Citronfläckad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucorrhinia pectoralis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lilla dammen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590524</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6513564</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>minst, kan säkert ha varit fler</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>126063813</v>
       </c>
       <c r="B3" t="n">
-        <v>45051</v>
+        <v>45052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>126063813</v>
       </c>
       <c r="B3" t="n">
-        <v>45052</v>
+        <v>45053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97217021</v>
+        <v>89818889</v>
       </c>
       <c r="B2" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100141</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,37 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra dammen, Ålberga Stenbrott, Nyängen, Srm</t>
+          <t>Oxelösund Hedenlunda, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590526.1620323915</v>
+        <v>589105</v>
       </c>
       <c r="R2" t="n">
-        <v>6513560.530149619</v>
+        <v>6515382</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -770,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,29 +763,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christopher Magnusson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christopher Magnusson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126063813</v>
+        <v>68710639</v>
       </c>
       <c r="B3" t="n">
-        <v>45053</v>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,50 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102918</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Citronfläckad kärrtrollslända</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucorrhinia pectoralis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Charpentier, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla dammen, Srm</t>
+          <t>En route, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590524</v>
+        <v>590416</v>
       </c>
       <c r="R3" t="n">
-        <v>6513564</v>
+        <v>6513846</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,17 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2017-03-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>minst, kan säkert ha varit fler</t>
+          <t>2017-03-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,22 +879,472 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Björn Anderson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Anderson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97217021</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58829</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södra dammen, Ålberga Stenbrott, Nyängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590526</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6513561</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-04-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-04-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Christopher Magnusson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Christopher Magnusson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126063813</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102918</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Citronfläckad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucorrhinia pectoralis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lilla dammen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590524</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6513564</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>minst, kan säkert ha varit fler</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89818880</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>588318</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6515575</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89818769</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>591348</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6512566</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,32 +1242,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89818769</v>
+        <v>135298774</v>
       </c>
       <c r="B7" t="n">
-        <v>102560</v>
+        <v>45306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222133</v>
+        <v>102918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Citronfläckad kärrtrollslända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Leucorrhinia pectoralis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Charpentier, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1275,16 +1275,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxelösund Hedenlunda, Srm</t>
+          <t>Nyängsdammen, Ålberga gård, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591348</v>
+        <v>590529</v>
       </c>
       <c r="R7" t="n">
-        <v>6512566</v>
+        <v>6513559</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,17 +1324,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>JMN0065 Calluna AB</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,21 +1348,128 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jan Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Gustafsson, Eva Edmert, Hans Norelius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89818769</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591348</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6512566</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Jonas Mattsson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Jonas Mattsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Gustafsson, Eva Edmert, Hans Norelius</t>
+          <t>Hans Norelius, Eva Edmert, Jan Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Norelius, Eva Edmert, Jan Gustafsson</t>
+          <t>Jan Gustafsson, Eva Edmert, Hans Norelius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818889</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818880</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68710639</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97217021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126063813</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298774</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,8 +1505,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -1275,7 +1275,7 @@
         <v>135298774</v>
       </c>
       <c r="B7" t="n">
-        <v>45306</v>
+        <v>45311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -1390,7 +1390,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Gustafsson, Eva Edmert, Hans Norelius</t>
+          <t>Hans Norelius, Eva Edmert, Jan Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -1390,7 +1390,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Norelius, Eva Edmert, Jan Gustafsson</t>
+          <t>Jan Gustafsson, Eva Edmert, Hans Norelius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 29797-2024 artfynd.xlsx
+++ b/artfynd/A 29797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1272,32 +1272,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89818769</v>
+        <v>135298774</v>
       </c>
       <c r="B7" t="n">
-        <v>102560</v>
+        <v>45311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222133</v>
+        <v>102918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Citronfläckad kärrtrollslända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Leucorrhinia pectoralis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Charpentier, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1305,16 +1305,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxelösund Hedenlunda, Srm</t>
+          <t>Nyängsdammen, Ålberga gård, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591348</v>
+        <v>590529</v>
       </c>
       <c r="R7" t="n">
-        <v>6512566</v>
+        <v>6513559</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,17 +1354,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>JMN0065 Calluna AB</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1378,134 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Jan Gustafsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Jan Gustafsson, Eva Edmert, Hans Norelius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298774</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89818769</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591348</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6512566</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89818769</t>
         </is>
@@ -1389,6 +1519,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
